--- a/data/forestry.xlsx
+++ b/data/forestry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuigalwayie-my.sharepoint.com/personal/0121302s_universityofgalway_ie/Documents/03. RESEARCH/01. LIVE PROEJCTS/CAMG Modelling/18. MODEL DEVELOPMENT/INTERFACE/Revisions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mim26609\PycharmProjects\OptiGOBTimeSeries\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECE4BA6C-925A-4942-815E-5B5F2AD55193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE26214-1C52-4591-9A95-D5831AAE331F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="4" activeTab="4" xr2:uid="{B86DC117-0B88-41ED-9D24-CA48C208C5B6}"/>
+    <workbookView xWindow="-76910" yWindow="-9680" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{B86DC117-0B88-41ED-9D24-CA48C208C5B6}"/>
   </bookViews>
   <sheets>
     <sheet name="existing_forest" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="51">
   <si>
     <t>metric</t>
   </si>
@@ -229,15 +229,6 @@
     <t>biomethane_energy</t>
   </si>
   <si>
-    <t>co2_emissions</t>
-  </si>
-  <si>
-    <t>ch4_emissions</t>
-  </si>
-  <si>
-    <t>n2o_emissions</t>
-  </si>
-  <si>
     <t>co2_substitution_credit</t>
   </si>
   <si>
@@ -262,9 +253,6 @@
     <t>grass_dry_matter</t>
   </si>
   <si>
-    <t>nh3_emissions</t>
-  </si>
-  <si>
     <t>n_to_water_emissions</t>
   </si>
   <si>
@@ -283,17 +271,26 @@
     <t>willow_dry_matter</t>
   </si>
   <si>
-    <t>lulucf_emissions_credit</t>
+    <t>co2</t>
   </si>
   <si>
-    <t>substitution_credit</t>
+    <t>ch4</t>
+  </si>
+  <si>
+    <t>n2o</t>
+  </si>
+  <si>
+    <t>nh3</t>
+  </si>
+  <si>
+    <t>lulucf_co2_emissions_credit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -355,7 +352,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -498,9 +495,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -538,7 +535,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -644,7 +641,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -786,7 +783,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -829,22 +826,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0594309-C3F3-4378-9548-578A61818027}">
   <dimension ref="A1:X89"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="6" customWidth="1"/>
-    <col min="2" max="4" width="8.7109375" style="6"/>
-    <col min="5" max="6" width="8.7109375" style="10"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" customWidth="1"/>
-    <col min="15" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="8.85546875" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" style="6" customWidth="1"/>
+    <col min="2" max="4" width="8.7265625" style="6"/>
+    <col min="5" max="6" width="8.7265625" style="10"/>
+    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.81640625" customWidth="1"/>
+    <col min="15" max="16" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.81640625" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="20" max="20" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" customHeight="1">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -918,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -992,7 +989,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -1066,7 +1063,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
@@ -1140,12 +1137,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="11" customFormat="1">
+    <row r="5" spans="1:24" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="11" customFormat="1">
+    <row r="6" spans="1:24" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>2020</v>
       </c>
@@ -1219,7 +1216,7 @@
         <v>-619.77964760800648</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="11" customFormat="1">
+    <row r="7" spans="1:24" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>2021</v>
       </c>
@@ -1293,7 +1290,7 @@
         <v>-619.77964760800648</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="11" customFormat="1">
+    <row r="8" spans="1:24" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>2022</v>
       </c>
@@ -1367,7 +1364,7 @@
         <v>-619.77964760800648</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="11" customFormat="1">
+    <row r="9" spans="1:24" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>2023</v>
       </c>
@@ -1441,7 +1438,7 @@
         <v>-619.77964760800648</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>2024</v>
       </c>
@@ -1515,7 +1512,7 @@
         <v>-619.77964760800648</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>2025</v>
       </c>
@@ -1589,7 +1586,7 @@
         <v>-893.38880082111029</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>2026</v>
       </c>
@@ -1663,7 +1660,7 @@
         <v>-878.52867619082838</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>2027</v>
       </c>
@@ -1737,7 +1734,7 @@
         <v>-843.85042036962034</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>2028</v>
       </c>
@@ -1811,7 +1808,7 @@
         <v>-838.57044353936283</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>2029</v>
       </c>
@@ -1885,7 +1882,7 @@
         <v>-836.95239991390213</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>2030</v>
       </c>
@@ -1959,7 +1956,7 @@
         <v>-1543.972509025082</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>2031</v>
       </c>
@@ -2033,7 +2030,7 @@
         <v>-1549.2889886618939</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>2032</v>
       </c>
@@ -2107,7 +2104,7 @@
         <v>-1519.0793196801033</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>2033</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>-1608.5030529961259</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>2034</v>
       </c>
@@ -2255,7 +2252,7 @@
         <v>-1813.4826590598302</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>2035</v>
       </c>
@@ -2329,7 +2326,7 @@
         <v>-1682.155450861015</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>2036</v>
       </c>
@@ -2403,7 +2400,7 @@
         <v>-1730.1485211162126</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>2037</v>
       </c>
@@ -2477,7 +2474,7 @@
         <v>-1785.8905520920277</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>2038</v>
       </c>
@@ -2551,7 +2548,7 @@
         <v>-1743.7834645663297</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>2039</v>
       </c>
@@ -2625,7 +2622,7 @@
         <v>-1801.4704875219165</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>2040</v>
       </c>
@@ -2699,7 +2696,7 @@
         <v>-1691.5236552038432</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>2041</v>
       </c>
@@ -2773,7 +2770,7 @@
         <v>-2023.3819676361381</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>2042</v>
       </c>
@@ -2847,7 +2844,7 @@
         <v>-1894.7352807000618</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>2043</v>
       </c>
@@ -2921,7 +2918,7 @@
         <v>-1848.4068759964423</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>2044</v>
       </c>
@@ -2995,7 +2992,7 @@
         <v>-1740.2347004784149</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>2045</v>
       </c>
@@ -3069,7 +3066,7 @@
         <v>-1689.1849243807817</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>2046</v>
       </c>
@@ -3143,7 +3140,7 @@
         <v>-1725.317160498317</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>2047</v>
       </c>
@@ -3217,7 +3214,7 @@
         <v>-1902.0147673273725</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>2048</v>
       </c>
@@ -3291,7 +3288,7 @@
         <v>-1915.3861280034191</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>2049</v>
       </c>
@@ -3365,7 +3362,7 @@
         <v>-1904.9220369624832</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>2050</v>
       </c>
@@ -3439,7 +3436,7 @@
         <v>-1869.55388201816</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>2051</v>
       </c>
@@ -3513,7 +3510,7 @@
         <v>-1895.0439146933902</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>2052</v>
       </c>
@@ -3587,7 +3584,7 @@
         <v>-1687.3237490884724</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>2053</v>
       </c>
@@ -3661,7 +3658,7 @@
         <v>-1679.7420651845005</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>2054</v>
       </c>
@@ -3735,7 +3732,7 @@
         <v>-1666.8736115903423</v>
       </c>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>2055</v>
       </c>
@@ -3809,7 +3806,7 @@
         <v>-1706.2308588729422</v>
       </c>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>2056</v>
       </c>
@@ -3883,7 +3880,7 @@
         <v>-1659.0058425446118</v>
       </c>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>2057</v>
       </c>
@@ -3957,7 +3954,7 @@
         <v>-1660.6238721780812</v>
       </c>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>2058</v>
       </c>
@@ -4031,7 +4028,7 @@
         <v>-1865.5534541172399</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>2059</v>
       </c>
@@ -4105,7 +4102,7 @@
         <v>-1869.7366147498371</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>2060</v>
       </c>
@@ -4179,7 +4176,7 @@
         <v>-1738.3561333312882</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>2061</v>
       </c>
@@ -4253,7 +4250,7 @@
         <v>-1766.0583755387015</v>
       </c>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>2062</v>
       </c>
@@ -4327,7 +4324,7 @@
         <v>-1747.3540825356113</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>2063</v>
       </c>
@@ -4401,7 +4398,7 @@
         <v>-1767.3154449958408</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>2064</v>
       </c>
@@ -4475,7 +4472,7 @@
         <v>-1615.8112231020962</v>
       </c>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>2065</v>
       </c>
@@ -4549,7 +4546,7 @@
         <v>-1727.9852453261949</v>
       </c>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>2066</v>
       </c>
@@ -4623,7 +4620,7 @@
         <v>-1666.6420174595394</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>2067</v>
       </c>
@@ -4697,7 +4694,7 @@
         <v>-1713.0944133200117</v>
       </c>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>2068</v>
       </c>
@@ -4771,7 +4768,7 @@
         <v>-2037.6105262665667</v>
       </c>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>2069</v>
       </c>
@@ -4845,7 +4842,7 @@
         <v>-1920.5168659398182</v>
       </c>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>2070</v>
       </c>
@@ -4919,7 +4916,7 @@
         <v>-2039.118068307575</v>
       </c>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>2071</v>
       </c>
@@ -4993,7 +4990,7 @@
         <v>-1846.2316678416448</v>
       </c>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>2072</v>
       </c>
@@ -5067,7 +5064,7 @@
         <v>-1805.6588703194745</v>
       </c>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>2073</v>
       </c>
@@ -5141,7 +5138,7 @@
         <v>-1781.1489976671835</v>
       </c>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>2074</v>
       </c>
@@ -5215,7 +5212,7 @@
         <v>-1923.9349913030076</v>
       </c>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>2075</v>
       </c>
@@ -5289,7 +5286,7 @@
         <v>-1985.8928125547238</v>
       </c>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>2076</v>
       </c>
@@ -5363,7 +5360,7 @@
         <v>-2135.8945975450483</v>
       </c>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>2077</v>
       </c>
@@ -5437,7 +5434,7 @@
         <v>-2036.1302315680516</v>
       </c>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>2078</v>
       </c>
@@ -5511,7 +5508,7 @@
         <v>-2013.3783382208619</v>
       </c>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>2079</v>
       </c>
@@ -5585,7 +5582,7 @@
         <v>-2025.8454194078752</v>
       </c>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>2080</v>
       </c>
@@ -5659,7 +5656,7 @@
         <v>-2059.7506387342551</v>
       </c>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>2081</v>
       </c>
@@ -5733,7 +5730,7 @@
         <v>-2095.3676439161845</v>
       </c>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>2082</v>
       </c>
@@ -5807,7 +5804,7 @@
         <v>-1998.7759058191459</v>
       </c>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>2083</v>
       </c>
@@ -5881,7 +5878,7 @@
         <v>-1924.9976177628787</v>
       </c>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>2084</v>
       </c>
@@ -5955,7 +5952,7 @@
         <v>-1906.0268234950902</v>
       </c>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>2085</v>
       </c>
@@ -6029,7 +6026,7 @@
         <v>-2176.7949634076058</v>
       </c>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>2086</v>
       </c>
@@ -6103,7 +6100,7 @@
         <v>-2101.5205755931161</v>
       </c>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>2087</v>
       </c>
@@ -6177,7 +6174,7 @@
         <v>-2060.7801572927983</v>
       </c>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>2088</v>
       </c>
@@ -6251,7 +6248,7 @@
         <v>-2025.7486216036737</v>
       </c>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>2089</v>
       </c>
@@ -6325,7 +6322,7 @@
         <v>-2059.3792866333474</v>
       </c>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>2090</v>
       </c>
@@ -6399,7 +6396,7 @@
         <v>-2040.9118040179105</v>
       </c>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>2091</v>
       </c>
@@ -6473,7 +6470,7 @@
         <v>-2014.6834983786857</v>
       </c>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>2092</v>
       </c>
@@ -6547,7 +6544,7 @@
         <v>-2131.2970841365677</v>
       </c>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>2093</v>
       </c>
@@ -6621,7 +6618,7 @@
         <v>-2218.6470941809439</v>
       </c>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>2094</v>
       </c>
@@ -6695,7 +6692,7 @@
         <v>-2078.1539123635198</v>
       </c>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>2095</v>
       </c>
@@ -6769,7 +6766,7 @@
         <v>-2110.6805709416076</v>
       </c>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>2096</v>
       </c>
@@ -6843,7 +6840,7 @@
         <v>-2169.2870634860519</v>
       </c>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>2097</v>
       </c>
@@ -6917,7 +6914,7 @@
         <v>-2158.0142970535312</v>
       </c>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>2098</v>
       </c>
@@ -6991,7 +6988,7 @@
         <v>-2107.7628237366821</v>
       </c>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>2099</v>
       </c>
@@ -7065,7 +7062,7 @@
         <v>-1969.718155251134</v>
       </c>
     </row>
-    <row r="86" spans="1:24">
+    <row r="86" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>2100</v>
       </c>
@@ -7139,14 +7136,14 @@
         <v>-1836.5144032785024</v>
       </c>
     </row>
-    <row r="87" spans="1:24">
+    <row r="87" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:24"/>
-    <row r="89" spans="1:24"/>
+    <row r="88" spans="1:24" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="89" spans="1:24" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7156,23 +7153,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2870A7D-6154-46B5-BE12-DA2643C3FE45}">
   <dimension ref="A1:BE90"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="6" customWidth="1"/>
-    <col min="3" max="6" width="8.7109375" style="6"/>
-    <col min="7" max="14" width="8.7109375" style="10"/>
-    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="30" width="8.85546875" customWidth="1"/>
-    <col min="31" max="32" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="38" width="8.85546875" customWidth="1"/>
-    <col min="39" max="40" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="9.7109375" customWidth="1"/>
-    <col min="43" max="44" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="8.7265625" style="6"/>
+    <col min="7" max="14" width="8.7265625" style="10"/>
+    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="30" width="8.81640625" customWidth="1"/>
+    <col min="31" max="32" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="38" width="8.81640625" customWidth="1"/>
+    <col min="39" max="40" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="9.7265625" customWidth="1"/>
+    <col min="43" max="44" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="15" customHeight="1">
+    <row r="1" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -7324,7 +7321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:57" s="3" customFormat="1">
+    <row r="2" spans="1:57" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
@@ -7476,7 +7473,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:57" s="3" customFormat="1">
+    <row r="3" spans="1:57" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -7628,7 +7625,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:57" s="3" customFormat="1">
+    <row r="4" spans="1:57" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -7780,7 +7777,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:57" s="3" customFormat="1">
+    <row r="5" spans="1:57" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
@@ -7932,7 +7929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:57" s="3" customFormat="1" ht="14.45" customHeight="1">
+    <row r="6" spans="1:57" s="3" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -8084,12 +8081,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:57" s="11" customFormat="1" ht="14.45" customHeight="1">
+    <row r="7" spans="1:57" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:57" s="11" customFormat="1" ht="14.45" customHeight="1">
+    <row r="8" spans="1:57" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>2020</v>
       </c>
@@ -8241,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:57" s="11" customFormat="1" ht="14.45" customHeight="1">
+    <row r="9" spans="1:57" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>2021</v>
       </c>
@@ -8393,7 +8390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:57" s="11" customFormat="1" ht="14.45" customHeight="1">
+    <row r="10" spans="1:57" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>2022</v>
       </c>
@@ -8545,7 +8542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:57" s="11" customFormat="1" ht="14.45" customHeight="1">
+    <row r="11" spans="1:57" s="11" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>2023</v>
       </c>
@@ -8697,7 +8694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:57">
+    <row r="12" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>2024</v>
       </c>
@@ -8855,7 +8852,7 @@
       <c r="BD12" s="7"/>
       <c r="BE12" s="7"/>
     </row>
-    <row r="13" spans="1:57">
+    <row r="13" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>2025</v>
       </c>
@@ -9013,7 +9010,7 @@
       <c r="BD13" s="7"/>
       <c r="BE13" s="7"/>
     </row>
-    <row r="14" spans="1:57">
+    <row r="14" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>2026</v>
       </c>
@@ -9171,7 +9168,7 @@
       <c r="BD14" s="7"/>
       <c r="BE14" s="7"/>
     </row>
-    <row r="15" spans="1:57">
+    <row r="15" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>2027</v>
       </c>
@@ -9329,7 +9326,7 @@
       <c r="BD15" s="7"/>
       <c r="BE15" s="7"/>
     </row>
-    <row r="16" spans="1:57">
+    <row r="16" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>2028</v>
       </c>
@@ -9487,7 +9484,7 @@
       <c r="BD16" s="7"/>
       <c r="BE16" s="7"/>
     </row>
-    <row r="17" spans="1:57">
+    <row r="17" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>2029</v>
       </c>
@@ -9645,7 +9642,7 @@
       <c r="BD17" s="7"/>
       <c r="BE17" s="7"/>
     </row>
-    <row r="18" spans="1:57">
+    <row r="18" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>2030</v>
       </c>
@@ -9803,7 +9800,7 @@
       <c r="BD18" s="7"/>
       <c r="BE18" s="7"/>
     </row>
-    <row r="19" spans="1:57">
+    <row r="19" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>2031</v>
       </c>
@@ -9961,7 +9958,7 @@
       <c r="BD19" s="7"/>
       <c r="BE19" s="7"/>
     </row>
-    <row r="20" spans="1:57">
+    <row r="20" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>2032</v>
       </c>
@@ -10119,7 +10116,7 @@
       <c r="BD20" s="7"/>
       <c r="BE20" s="7"/>
     </row>
-    <row r="21" spans="1:57">
+    <row r="21" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>2033</v>
       </c>
@@ -10277,7 +10274,7 @@
       <c r="BD21" s="7"/>
       <c r="BE21" s="7"/>
     </row>
-    <row r="22" spans="1:57">
+    <row r="22" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>2034</v>
       </c>
@@ -10435,7 +10432,7 @@
       <c r="BD22" s="7"/>
       <c r="BE22" s="7"/>
     </row>
-    <row r="23" spans="1:57">
+    <row r="23" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>2035</v>
       </c>
@@ -10593,7 +10590,7 @@
       <c r="BD23" s="7"/>
       <c r="BE23" s="7"/>
     </row>
-    <row r="24" spans="1:57">
+    <row r="24" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>2036</v>
       </c>
@@ -10751,7 +10748,7 @@
       <c r="BD24" s="7"/>
       <c r="BE24" s="7"/>
     </row>
-    <row r="25" spans="1:57">
+    <row r="25" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>2037</v>
       </c>
@@ -10909,7 +10906,7 @@
       <c r="BD25" s="7"/>
       <c r="BE25" s="7"/>
     </row>
-    <row r="26" spans="1:57">
+    <row r="26" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>2038</v>
       </c>
@@ -11067,7 +11064,7 @@
       <c r="BD26" s="7"/>
       <c r="BE26" s="7"/>
     </row>
-    <row r="27" spans="1:57">
+    <row r="27" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>2039</v>
       </c>
@@ -11225,7 +11222,7 @@
       <c r="BD27" s="7"/>
       <c r="BE27" s="7"/>
     </row>
-    <row r="28" spans="1:57">
+    <row r="28" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>2040</v>
       </c>
@@ -11383,7 +11380,7 @@
       <c r="BD28" s="7"/>
       <c r="BE28" s="7"/>
     </row>
-    <row r="29" spans="1:57">
+    <row r="29" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>2041</v>
       </c>
@@ -11541,7 +11538,7 @@
       <c r="BD29" s="7"/>
       <c r="BE29" s="7"/>
     </row>
-    <row r="30" spans="1:57">
+    <row r="30" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>2042</v>
       </c>
@@ -11699,7 +11696,7 @@
       <c r="BD30" s="7"/>
       <c r="BE30" s="7"/>
     </row>
-    <row r="31" spans="1:57">
+    <row r="31" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>2043</v>
       </c>
@@ -11857,7 +11854,7 @@
       <c r="BD31" s="7"/>
       <c r="BE31" s="7"/>
     </row>
-    <row r="32" spans="1:57">
+    <row r="32" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>2044</v>
       </c>
@@ -12015,7 +12012,7 @@
       <c r="BD32" s="7"/>
       <c r="BE32" s="7"/>
     </row>
-    <row r="33" spans="1:57">
+    <row r="33" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>2045</v>
       </c>
@@ -12173,7 +12170,7 @@
       <c r="BD33" s="7"/>
       <c r="BE33" s="7"/>
     </row>
-    <row r="34" spans="1:57">
+    <row r="34" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>2046</v>
       </c>
@@ -12331,7 +12328,7 @@
       <c r="BD34" s="7"/>
       <c r="BE34" s="7"/>
     </row>
-    <row r="35" spans="1:57">
+    <row r="35" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>2047</v>
       </c>
@@ -12489,7 +12486,7 @@
       <c r="BD35" s="7"/>
       <c r="BE35" s="7"/>
     </row>
-    <row r="36" spans="1:57">
+    <row r="36" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>2048</v>
       </c>
@@ -12647,7 +12644,7 @@
       <c r="BD36" s="7"/>
       <c r="BE36" s="7"/>
     </row>
-    <row r="37" spans="1:57">
+    <row r="37" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>2049</v>
       </c>
@@ -12805,7 +12802,7 @@
       <c r="BD37" s="7"/>
       <c r="BE37" s="7"/>
     </row>
-    <row r="38" spans="1:57">
+    <row r="38" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>2050</v>
       </c>
@@ -12963,7 +12960,7 @@
       <c r="BD38" s="7"/>
       <c r="BE38" s="7"/>
     </row>
-    <row r="39" spans="1:57">
+    <row r="39" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>2051</v>
       </c>
@@ -13121,7 +13118,7 @@
       <c r="BD39" s="7"/>
       <c r="BE39" s="7"/>
     </row>
-    <row r="40" spans="1:57">
+    <row r="40" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>2052</v>
       </c>
@@ -13279,7 +13276,7 @@
       <c r="BD40" s="7"/>
       <c r="BE40" s="7"/>
     </row>
-    <row r="41" spans="1:57">
+    <row r="41" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>2053</v>
       </c>
@@ -13437,7 +13434,7 @@
       <c r="BD41" s="7"/>
       <c r="BE41" s="7"/>
     </row>
-    <row r="42" spans="1:57">
+    <row r="42" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>2054</v>
       </c>
@@ -13595,7 +13592,7 @@
       <c r="BD42" s="7"/>
       <c r="BE42" s="7"/>
     </row>
-    <row r="43" spans="1:57">
+    <row r="43" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>2055</v>
       </c>
@@ -13753,7 +13750,7 @@
       <c r="BD43" s="7"/>
       <c r="BE43" s="7"/>
     </row>
-    <row r="44" spans="1:57">
+    <row r="44" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>2056</v>
       </c>
@@ -13911,7 +13908,7 @@
       <c r="BD44" s="7"/>
       <c r="BE44" s="7"/>
     </row>
-    <row r="45" spans="1:57">
+    <row r="45" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>2057</v>
       </c>
@@ -14069,7 +14066,7 @@
       <c r="BD45" s="7"/>
       <c r="BE45" s="7"/>
     </row>
-    <row r="46" spans="1:57">
+    <row r="46" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>2058</v>
       </c>
@@ -14227,7 +14224,7 @@
       <c r="BD46" s="7"/>
       <c r="BE46" s="7"/>
     </row>
-    <row r="47" spans="1:57">
+    <row r="47" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>2059</v>
       </c>
@@ -14385,7 +14382,7 @@
       <c r="BD47" s="7"/>
       <c r="BE47" s="7"/>
     </row>
-    <row r="48" spans="1:57">
+    <row r="48" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>2060</v>
       </c>
@@ -14543,7 +14540,7 @@
       <c r="BD48" s="7"/>
       <c r="BE48" s="7"/>
     </row>
-    <row r="49" spans="1:57">
+    <row r="49" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>2061</v>
       </c>
@@ -14701,7 +14698,7 @@
       <c r="BD49" s="7"/>
       <c r="BE49" s="7"/>
     </row>
-    <row r="50" spans="1:57">
+    <row r="50" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>2062</v>
       </c>
@@ -14859,7 +14856,7 @@
       <c r="BD50" s="7"/>
       <c r="BE50" s="7"/>
     </row>
-    <row r="51" spans="1:57">
+    <row r="51" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>2063</v>
       </c>
@@ -15017,7 +15014,7 @@
       <c r="BD51" s="7"/>
       <c r="BE51" s="7"/>
     </row>
-    <row r="52" spans="1:57">
+    <row r="52" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>2064</v>
       </c>
@@ -15175,7 +15172,7 @@
       <c r="BD52" s="7"/>
       <c r="BE52" s="7"/>
     </row>
-    <row r="53" spans="1:57">
+    <row r="53" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>2065</v>
       </c>
@@ -15333,7 +15330,7 @@
       <c r="BD53" s="7"/>
       <c r="BE53" s="7"/>
     </row>
-    <row r="54" spans="1:57">
+    <row r="54" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>2066</v>
       </c>
@@ -15491,7 +15488,7 @@
       <c r="BD54" s="7"/>
       <c r="BE54" s="7"/>
     </row>
-    <row r="55" spans="1:57">
+    <row r="55" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>2067</v>
       </c>
@@ -15649,7 +15646,7 @@
       <c r="BD55" s="7"/>
       <c r="BE55" s="7"/>
     </row>
-    <row r="56" spans="1:57">
+    <row r="56" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>2068</v>
       </c>
@@ -15807,7 +15804,7 @@
       <c r="BD56" s="7"/>
       <c r="BE56" s="7"/>
     </row>
-    <row r="57" spans="1:57">
+    <row r="57" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>2069</v>
       </c>
@@ -15965,7 +15962,7 @@
       <c r="BD57" s="7"/>
       <c r="BE57" s="7"/>
     </row>
-    <row r="58" spans="1:57">
+    <row r="58" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>2070</v>
       </c>
@@ -16123,7 +16120,7 @@
       <c r="BD58" s="7"/>
       <c r="BE58" s="7"/>
     </row>
-    <row r="59" spans="1:57">
+    <row r="59" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>2071</v>
       </c>
@@ -16281,7 +16278,7 @@
       <c r="BD59" s="7"/>
       <c r="BE59" s="7"/>
     </row>
-    <row r="60" spans="1:57">
+    <row r="60" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>2072</v>
       </c>
@@ -16439,7 +16436,7 @@
       <c r="BD60" s="7"/>
       <c r="BE60" s="7"/>
     </row>
-    <row r="61" spans="1:57">
+    <row r="61" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>2073</v>
       </c>
@@ -16597,7 +16594,7 @@
       <c r="BD61" s="7"/>
       <c r="BE61" s="7"/>
     </row>
-    <row r="62" spans="1:57">
+    <row r="62" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>2074</v>
       </c>
@@ -16755,7 +16752,7 @@
       <c r="BD62" s="7"/>
       <c r="BE62" s="7"/>
     </row>
-    <row r="63" spans="1:57">
+    <row r="63" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>2075</v>
       </c>
@@ -16913,7 +16910,7 @@
       <c r="BD63" s="7"/>
       <c r="BE63" s="7"/>
     </row>
-    <row r="64" spans="1:57">
+    <row r="64" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>2076</v>
       </c>
@@ -17071,7 +17068,7 @@
       <c r="BD64" s="7"/>
       <c r="BE64" s="7"/>
     </row>
-    <row r="65" spans="1:57">
+    <row r="65" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>2077</v>
       </c>
@@ -17229,7 +17226,7 @@
       <c r="BD65" s="7"/>
       <c r="BE65" s="7"/>
     </row>
-    <row r="66" spans="1:57">
+    <row r="66" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>2078</v>
       </c>
@@ -17387,7 +17384,7 @@
       <c r="BD66" s="7"/>
       <c r="BE66" s="7"/>
     </row>
-    <row r="67" spans="1:57">
+    <row r="67" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>2079</v>
       </c>
@@ -17545,7 +17542,7 @@
       <c r="BD67" s="7"/>
       <c r="BE67" s="7"/>
     </row>
-    <row r="68" spans="1:57">
+    <row r="68" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>2080</v>
       </c>
@@ -17703,7 +17700,7 @@
       <c r="BD68" s="7"/>
       <c r="BE68" s="7"/>
     </row>
-    <row r="69" spans="1:57">
+    <row r="69" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>2081</v>
       </c>
@@ -17861,7 +17858,7 @@
       <c r="BD69" s="7"/>
       <c r="BE69" s="7"/>
     </row>
-    <row r="70" spans="1:57">
+    <row r="70" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>2082</v>
       </c>
@@ -18019,7 +18016,7 @@
       <c r="BD70" s="7"/>
       <c r="BE70" s="7"/>
     </row>
-    <row r="71" spans="1:57">
+    <row r="71" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>2083</v>
       </c>
@@ -18177,7 +18174,7 @@
       <c r="BD71" s="7"/>
       <c r="BE71" s="7"/>
     </row>
-    <row r="72" spans="1:57">
+    <row r="72" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>2084</v>
       </c>
@@ -18335,7 +18332,7 @@
       <c r="BD72" s="7"/>
       <c r="BE72" s="7"/>
     </row>
-    <row r="73" spans="1:57">
+    <row r="73" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>2085</v>
       </c>
@@ -18493,7 +18490,7 @@
       <c r="BD73" s="7"/>
       <c r="BE73" s="7"/>
     </row>
-    <row r="74" spans="1:57">
+    <row r="74" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>2086</v>
       </c>
@@ -18651,7 +18648,7 @@
       <c r="BD74" s="7"/>
       <c r="BE74" s="7"/>
     </row>
-    <row r="75" spans="1:57">
+    <row r="75" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>2087</v>
       </c>
@@ -18809,7 +18806,7 @@
       <c r="BD75" s="7"/>
       <c r="BE75" s="7"/>
     </row>
-    <row r="76" spans="1:57">
+    <row r="76" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>2088</v>
       </c>
@@ -18967,7 +18964,7 @@
       <c r="BD76" s="7"/>
       <c r="BE76" s="7"/>
     </row>
-    <row r="77" spans="1:57">
+    <row r="77" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>2089</v>
       </c>
@@ -19125,7 +19122,7 @@
       <c r="BD77" s="7"/>
       <c r="BE77" s="7"/>
     </row>
-    <row r="78" spans="1:57">
+    <row r="78" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>2090</v>
       </c>
@@ -19283,7 +19280,7 @@
       <c r="BD78" s="7"/>
       <c r="BE78" s="7"/>
     </row>
-    <row r="79" spans="1:57">
+    <row r="79" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>2091</v>
       </c>
@@ -19441,7 +19438,7 @@
       <c r="BD79" s="7"/>
       <c r="BE79" s="7"/>
     </row>
-    <row r="80" spans="1:57">
+    <row r="80" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>2092</v>
       </c>
@@ -19599,7 +19596,7 @@
       <c r="BD80" s="7"/>
       <c r="BE80" s="7"/>
     </row>
-    <row r="81" spans="1:57">
+    <row r="81" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>2093</v>
       </c>
@@ -19757,7 +19754,7 @@
       <c r="BD81" s="7"/>
       <c r="BE81" s="7"/>
     </row>
-    <row r="82" spans="1:57">
+    <row r="82" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>2094</v>
       </c>
@@ -19915,7 +19912,7 @@
       <c r="BD82" s="7"/>
       <c r="BE82" s="7"/>
     </row>
-    <row r="83" spans="1:57">
+    <row r="83" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>2095</v>
       </c>
@@ -20073,7 +20070,7 @@
       <c r="BD83" s="7"/>
       <c r="BE83" s="7"/>
     </row>
-    <row r="84" spans="1:57">
+    <row r="84" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>2096</v>
       </c>
@@ -20231,7 +20228,7 @@
       <c r="BD84" s="7"/>
       <c r="BE84" s="7"/>
     </row>
-    <row r="85" spans="1:57">
+    <row r="85" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>2097</v>
       </c>
@@ -20389,7 +20386,7 @@
       <c r="BD85" s="7"/>
       <c r="BE85" s="7"/>
     </row>
-    <row r="86" spans="1:57">
+    <row r="86" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="6">
         <v>2098</v>
       </c>
@@ -20547,7 +20544,7 @@
       <c r="BD86" s="7"/>
       <c r="BE86" s="7"/>
     </row>
-    <row r="87" spans="1:57">
+    <row r="87" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>2099</v>
       </c>
@@ -20705,7 +20702,7 @@
       <c r="BD87" s="7"/>
       <c r="BE87" s="7"/>
     </row>
-    <row r="88" spans="1:57">
+    <row r="88" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>2100</v>
       </c>
@@ -20863,7 +20860,7 @@
       <c r="BD88" s="7"/>
       <c r="BE88" s="7"/>
     </row>
-    <row r="89" spans="1:57">
+    <row r="89" spans="1:57" ht="14.5" x14ac:dyDescent="0.35">
       <c r="K89" s="9"/>
       <c r="L89" s="9"/>
       <c r="M89" s="9"/>
@@ -20877,7 +20874,7 @@
       <c r="U89" s="7"/>
       <c r="V89" s="7"/>
     </row>
-    <row r="90" spans="1:57"/>
+    <row r="90" spans="1:57" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20887,9 +20884,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2624EDC8-A824-4B64-A342-68816A2A7554}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -20903,7 +20903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -20917,7 +20917,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -20931,7 +20931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -20959,7 +20959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -20973,7 +20973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -20987,7 +20987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -21001,7 +21001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -21015,7 +21015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -21029,7 +21029,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -21051,9 +21051,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0890E3-5A87-4964-A460-B7480D8C3A7A}">
   <dimension ref="A1:X85"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -21067,37 +21067,37 @@
         <v>2</v>
       </c>
       <c r="E1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="K1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="P1" s="11"/>
       <c r="Q1" s="11"/>
@@ -21109,7 +21109,7 @@
       <c r="W1" s="11"/>
       <c r="X1" s="11"/>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -21165,12 +21165,12 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>12</v>
@@ -21179,37 +21179,37 @@
         <v>12</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
@@ -21221,7 +21221,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>23</v>
       </c>
@@ -21248,7 +21248,7 @@
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>2020</v>
       </c>
@@ -21304,7 +21304,7 @@
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>2021</v>
       </c>
@@ -21360,7 +21360,7 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>2022</v>
       </c>
@@ -21416,7 +21416,7 @@
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>2023</v>
       </c>
@@ -21472,7 +21472,7 @@
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>2024</v>
       </c>
@@ -21528,7 +21528,7 @@
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>2025</v>
       </c>
@@ -21584,7 +21584,7 @@
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>2026</v>
       </c>
@@ -21640,7 +21640,7 @@
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>2027</v>
       </c>
@@ -21696,7 +21696,7 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
         <v>2028</v>
       </c>
@@ -21752,7 +21752,7 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
         <v>2029</v>
       </c>
@@ -21808,7 +21808,7 @@
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>2030</v>
       </c>
@@ -21864,7 +21864,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="6">
         <v>2031</v>
       </c>
@@ -21920,7 +21920,7 @@
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
         <v>2032</v>
       </c>
@@ -21976,7 +21976,7 @@
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>2033</v>
       </c>
@@ -22032,7 +22032,7 @@
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>2034</v>
       </c>
@@ -22088,7 +22088,7 @@
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="6">
         <v>2035</v>
       </c>
@@ -22144,7 +22144,7 @@
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>2036</v>
       </c>
@@ -22200,7 +22200,7 @@
       <c r="W21" s="7"/>
       <c r="X21" s="7"/>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
         <v>2037</v>
       </c>
@@ -22256,7 +22256,7 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
         <v>2038</v>
       </c>
@@ -22312,7 +22312,7 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>2039</v>
       </c>
@@ -22368,7 +22368,7 @@
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" s="6">
         <v>2040</v>
       </c>
@@ -22424,7 +22424,7 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" s="6">
         <v>2041</v>
       </c>
@@ -22480,7 +22480,7 @@
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>2042</v>
       </c>
@@ -22536,7 +22536,7 @@
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="6">
         <v>2043</v>
       </c>
@@ -22592,7 +22592,7 @@
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" s="6">
         <v>2044</v>
       </c>
@@ -22648,7 +22648,7 @@
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>2045</v>
       </c>
@@ -22704,7 +22704,7 @@
       <c r="W30" s="7"/>
       <c r="X30" s="7"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" s="6">
         <v>2046</v>
       </c>
@@ -22760,7 +22760,7 @@
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" s="6">
         <v>2047</v>
       </c>
@@ -22816,7 +22816,7 @@
       <c r="W32" s="7"/>
       <c r="X32" s="7"/>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>2048</v>
       </c>
@@ -22872,7 +22872,7 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" s="6">
         <v>2049</v>
       </c>
@@ -22928,7 +22928,7 @@
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" s="6">
         <v>2050</v>
       </c>
@@ -22984,7 +22984,7 @@
       <c r="W35" s="7"/>
       <c r="X35" s="7"/>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>2051</v>
       </c>
@@ -23040,7 +23040,7 @@
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37" s="6">
         <v>2052</v>
       </c>
@@ -23096,7 +23096,7 @@
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" s="6">
         <v>2053</v>
       </c>
@@ -23152,7 +23152,7 @@
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>2054</v>
       </c>
@@ -23208,7 +23208,7 @@
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40" s="6">
         <v>2055</v>
       </c>
@@ -23264,7 +23264,7 @@
       <c r="W40" s="7"/>
       <c r="X40" s="7"/>
     </row>
-    <row r="41" spans="1:24">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" s="6">
         <v>2056</v>
       </c>
@@ -23320,7 +23320,7 @@
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
     </row>
-    <row r="42" spans="1:24">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>2057</v>
       </c>
@@ -23376,7 +23376,7 @@
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
     </row>
-    <row r="43" spans="1:24">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" s="6">
         <v>2058</v>
       </c>
@@ -23432,7 +23432,7 @@
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
     </row>
-    <row r="44" spans="1:24">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" s="6">
         <v>2059</v>
       </c>
@@ -23488,7 +23488,7 @@
       <c r="W44" s="7"/>
       <c r="X44" s="7"/>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>2060</v>
       </c>
@@ -23544,7 +23544,7 @@
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" s="6">
         <v>2061</v>
       </c>
@@ -23600,7 +23600,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" s="6">
         <v>2062</v>
       </c>
@@ -23656,7 +23656,7 @@
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
     </row>
-    <row r="48" spans="1:24">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>2063</v>
       </c>
@@ -23712,7 +23712,7 @@
       <c r="W48" s="7"/>
       <c r="X48" s="7"/>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" s="6">
         <v>2064</v>
       </c>
@@ -23768,7 +23768,7 @@
       <c r="W49" s="7"/>
       <c r="X49" s="7"/>
     </row>
-    <row r="50" spans="1:24">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50" s="6">
         <v>2065</v>
       </c>
@@ -23824,7 +23824,7 @@
       <c r="W50" s="7"/>
       <c r="X50" s="7"/>
     </row>
-    <row r="51" spans="1:24">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>2066</v>
       </c>
@@ -23880,7 +23880,7 @@
       <c r="W51" s="7"/>
       <c r="X51" s="7"/>
     </row>
-    <row r="52" spans="1:24">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52" s="6">
         <v>2067</v>
       </c>
@@ -23936,7 +23936,7 @@
       <c r="W52" s="7"/>
       <c r="X52" s="7"/>
     </row>
-    <row r="53" spans="1:24">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A53" s="6">
         <v>2068</v>
       </c>
@@ -23992,7 +23992,7 @@
       <c r="W53" s="7"/>
       <c r="X53" s="7"/>
     </row>
-    <row r="54" spans="1:24">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>2069</v>
       </c>
@@ -24048,7 +24048,7 @@
       <c r="W54" s="7"/>
       <c r="X54" s="7"/>
     </row>
-    <row r="55" spans="1:24">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55" s="6">
         <v>2070</v>
       </c>
@@ -24104,7 +24104,7 @@
       <c r="W55" s="7"/>
       <c r="X55" s="7"/>
     </row>
-    <row r="56" spans="1:24">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56" s="6">
         <v>2071</v>
       </c>
@@ -24160,7 +24160,7 @@
       <c r="W56" s="7"/>
       <c r="X56" s="7"/>
     </row>
-    <row r="57" spans="1:24">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>2072</v>
       </c>
@@ -24216,7 +24216,7 @@
       <c r="W57" s="7"/>
       <c r="X57" s="7"/>
     </row>
-    <row r="58" spans="1:24">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58" s="6">
         <v>2073</v>
       </c>
@@ -24272,7 +24272,7 @@
       <c r="W58" s="7"/>
       <c r="X58" s="7"/>
     </row>
-    <row r="59" spans="1:24">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59" s="6">
         <v>2074</v>
       </c>
@@ -24328,7 +24328,7 @@
       <c r="W59" s="7"/>
       <c r="X59" s="7"/>
     </row>
-    <row r="60" spans="1:24">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>2075</v>
       </c>
@@ -24384,7 +24384,7 @@
       <c r="W60" s="7"/>
       <c r="X60" s="7"/>
     </row>
-    <row r="61" spans="1:24">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61" s="6">
         <v>2076</v>
       </c>
@@ -24440,7 +24440,7 @@
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
     </row>
-    <row r="62" spans="1:24">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62" s="6">
         <v>2077</v>
       </c>
@@ -24496,7 +24496,7 @@
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
     </row>
-    <row r="63" spans="1:24">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>2078</v>
       </c>
@@ -24552,7 +24552,7 @@
       <c r="W63" s="7"/>
       <c r="X63" s="7"/>
     </row>
-    <row r="64" spans="1:24">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64" s="6">
         <v>2079</v>
       </c>
@@ -24608,7 +24608,7 @@
       <c r="W64" s="7"/>
       <c r="X64" s="7"/>
     </row>
-    <row r="65" spans="1:24">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A65" s="6">
         <v>2080</v>
       </c>
@@ -24664,7 +24664,7 @@
       <c r="W65" s="7"/>
       <c r="X65" s="7"/>
     </row>
-    <row r="66" spans="1:24">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>2081</v>
       </c>
@@ -24720,7 +24720,7 @@
       <c r="W66" s="7"/>
       <c r="X66" s="7"/>
     </row>
-    <row r="67" spans="1:24">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A67" s="6">
         <v>2082</v>
       </c>
@@ -24776,7 +24776,7 @@
       <c r="W67" s="7"/>
       <c r="X67" s="7"/>
     </row>
-    <row r="68" spans="1:24">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A68" s="6">
         <v>2083</v>
       </c>
@@ -24832,7 +24832,7 @@
       <c r="W68" s="7"/>
       <c r="X68" s="7"/>
     </row>
-    <row r="69" spans="1:24">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>2084</v>
       </c>
@@ -24888,7 +24888,7 @@
       <c r="W69" s="7"/>
       <c r="X69" s="7"/>
     </row>
-    <row r="70" spans="1:24">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A70" s="6">
         <v>2085</v>
       </c>
@@ -24944,7 +24944,7 @@
       <c r="W70" s="7"/>
       <c r="X70" s="7"/>
     </row>
-    <row r="71" spans="1:24">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A71" s="6">
         <v>2086</v>
       </c>
@@ -25000,7 +25000,7 @@
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
     </row>
-    <row r="72" spans="1:24">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>2087</v>
       </c>
@@ -25056,7 +25056,7 @@
       <c r="W72" s="7"/>
       <c r="X72" s="7"/>
     </row>
-    <row r="73" spans="1:24">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A73" s="6">
         <v>2088</v>
       </c>
@@ -25112,7 +25112,7 @@
       <c r="W73" s="7"/>
       <c r="X73" s="7"/>
     </row>
-    <row r="74" spans="1:24">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A74" s="6">
         <v>2089</v>
       </c>
@@ -25168,7 +25168,7 @@
       <c r="W74" s="7"/>
       <c r="X74" s="7"/>
     </row>
-    <row r="75" spans="1:24">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>2090</v>
       </c>
@@ -25224,7 +25224,7 @@
       <c r="W75" s="7"/>
       <c r="X75" s="7"/>
     </row>
-    <row r="76" spans="1:24">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A76" s="6">
         <v>2091</v>
       </c>
@@ -25280,7 +25280,7 @@
       <c r="W76" s="7"/>
       <c r="X76" s="7"/>
     </row>
-    <row r="77" spans="1:24">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A77" s="6">
         <v>2092</v>
       </c>
@@ -25336,7 +25336,7 @@
       <c r="W77" s="7"/>
       <c r="X77" s="7"/>
     </row>
-    <row r="78" spans="1:24">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>2093</v>
       </c>
@@ -25392,7 +25392,7 @@
       <c r="W78" s="7"/>
       <c r="X78" s="7"/>
     </row>
-    <row r="79" spans="1:24">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A79" s="6">
         <v>2094</v>
       </c>
@@ -25448,7 +25448,7 @@
       <c r="W79" s="7"/>
       <c r="X79" s="7"/>
     </row>
-    <row r="80" spans="1:24">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A80" s="6">
         <v>2095</v>
       </c>
@@ -25504,7 +25504,7 @@
       <c r="W80" s="7"/>
       <c r="X80" s="7"/>
     </row>
-    <row r="81" spans="1:24">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>2096</v>
       </c>
@@ -25560,7 +25560,7 @@
       <c r="W81" s="7"/>
       <c r="X81" s="7"/>
     </row>
-    <row r="82" spans="1:24">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A82" s="6">
         <v>2097</v>
       </c>
@@ -25616,7 +25616,7 @@
       <c r="W82" s="7"/>
       <c r="X82" s="7"/>
     </row>
-    <row r="83" spans="1:24">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A83" s="6">
         <v>2098</v>
       </c>
@@ -25672,7 +25672,7 @@
       <c r="W83" s="7"/>
       <c r="X83" s="7"/>
     </row>
-    <row r="84" spans="1:24">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>2099</v>
       </c>
@@ -25728,7 +25728,7 @@
       <c r="W84" s="7"/>
       <c r="X84" s="7"/>
     </row>
-    <row r="85" spans="1:24">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A85" s="6">
         <v>2100</v>
       </c>
@@ -25792,9 +25792,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34836405-4481-4BAF-9772-C50480C7C417}">
   <dimension ref="A1:S86"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="45.75" customHeight="1">
+    <row r="1" spans="1:19" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -25802,7 +25802,7 @@
         <v>31</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>1</v>
@@ -25811,28 +25811,28 @@
         <v>2</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N1" s="17" t="s">
         <v>7</v>
@@ -25845,7 +25845,7 @@
       <c r="R1" s="18"/>
       <c r="S1" s="18"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>20</v>
       </c>
@@ -25896,15 +25896,15 @@
       <c r="R2" s="18"/>
       <c r="S2" s="18"/>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>12</v>
@@ -25913,41 +25913,41 @@
         <v>12</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N3" s="22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O3" s="22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P3" s="23"/>
       <c r="Q3" s="23"/>
       <c r="R3" s="23"/>
       <c r="S3" s="23"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>23</v>
       </c>
@@ -25970,7 +25970,7 @@
       <c r="R4" s="18"/>
       <c r="S4" s="18"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="20">
         <v>2020</v>
       </c>
@@ -26021,7 +26021,7 @@
       <c r="R5" s="23"/>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="20">
         <v>2021</v>
       </c>
@@ -26072,7 +26072,7 @@
       <c r="R6" s="23"/>
       <c r="S6" s="23"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="20">
         <v>2022</v>
       </c>
@@ -26123,7 +26123,7 @@
       <c r="R7" s="23"/>
       <c r="S7" s="23"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="20">
         <v>2023</v>
       </c>
@@ -26174,7 +26174,7 @@
       <c r="R8" s="23"/>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="20">
         <v>2024</v>
       </c>
@@ -26225,7 +26225,7 @@
       <c r="R9" s="23"/>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="20">
         <v>2025</v>
       </c>
@@ -26276,7 +26276,7 @@
       <c r="R10" s="23"/>
       <c r="S10" s="23"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="20">
         <v>2026</v>
       </c>
@@ -26327,7 +26327,7 @@
       <c r="R11" s="23"/>
       <c r="S11" s="23"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="20">
         <v>2027</v>
       </c>
@@ -26378,7 +26378,7 @@
       <c r="R12" s="23"/>
       <c r="S12" s="23"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="20">
         <v>2028</v>
       </c>
@@ -26429,7 +26429,7 @@
       <c r="R13" s="23"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
         <v>2029</v>
       </c>
@@ -26480,7 +26480,7 @@
       <c r="R14" s="23"/>
       <c r="S14" s="23"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="20">
         <v>2030</v>
       </c>
@@ -26531,7 +26531,7 @@
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="20">
         <v>2031</v>
       </c>
@@ -26582,7 +26582,7 @@
       <c r="R16" s="23"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="20">
         <v>2032</v>
       </c>
@@ -26633,7 +26633,7 @@
       <c r="R17" s="23"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="20">
         <v>2033</v>
       </c>
@@ -26684,7 +26684,7 @@
       <c r="R18" s="23"/>
       <c r="S18" s="23"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="20">
         <v>2034</v>
       </c>
@@ -26735,7 +26735,7 @@
       <c r="R19" s="23"/>
       <c r="S19" s="23"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="20">
         <v>2035</v>
       </c>
@@ -26786,7 +26786,7 @@
       <c r="R20" s="36"/>
       <c r="S20" s="23"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="20">
         <v>2036</v>
       </c>
@@ -26837,7 +26837,7 @@
       <c r="R21" s="23"/>
       <c r="S21" s="23"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="20">
         <v>2037</v>
       </c>
@@ -26888,7 +26888,7 @@
       <c r="R22" s="23"/>
       <c r="S22" s="23"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
         <v>2038</v>
       </c>
@@ -26939,7 +26939,7 @@
       <c r="R23" s="23"/>
       <c r="S23" s="23"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="20">
         <v>2039</v>
       </c>
@@ -26990,7 +26990,7 @@
       <c r="R24" s="23"/>
       <c r="S24" s="23"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="20">
         <v>2040</v>
       </c>
@@ -27041,7 +27041,7 @@
       <c r="R25" s="23"/>
       <c r="S25" s="23"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
         <v>2041</v>
       </c>
@@ -27092,7 +27092,7 @@
       <c r="R26" s="23"/>
       <c r="S26" s="23"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="20">
         <v>2042</v>
       </c>
@@ -27143,7 +27143,7 @@
       <c r="R27" s="23"/>
       <c r="S27" s="23"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="20">
         <v>2043</v>
       </c>
@@ -27194,7 +27194,7 @@
       <c r="R28" s="23"/>
       <c r="S28" s="23"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="20">
         <v>2044</v>
       </c>
@@ -27245,7 +27245,7 @@
       <c r="R29" s="23"/>
       <c r="S29" s="23"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="20">
         <v>2045</v>
       </c>
@@ -27296,7 +27296,7 @@
       <c r="R30" s="23"/>
       <c r="S30" s="23"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="20">
         <v>2046</v>
       </c>
@@ -27347,7 +27347,7 @@
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
         <v>2047</v>
       </c>
@@ -27398,7 +27398,7 @@
       <c r="R32" s="23"/>
       <c r="S32" s="23"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
         <v>2048</v>
       </c>
@@ -27449,7 +27449,7 @@
       <c r="R33" s="23"/>
       <c r="S33" s="23"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
         <v>2049</v>
       </c>
@@ -27500,7 +27500,7 @@
       <c r="R34" s="23"/>
       <c r="S34" s="23"/>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="20">
         <v>2050</v>
       </c>
@@ -27551,7 +27551,7 @@
       <c r="R35" s="23"/>
       <c r="S35" s="23"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="20">
         <v>2051</v>
       </c>
@@ -27602,7 +27602,7 @@
       <c r="R36" s="23"/>
       <c r="S36" s="23"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="20">
         <v>2052</v>
       </c>
@@ -27653,7 +27653,7 @@
       <c r="R37" s="23"/>
       <c r="S37" s="23"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="20">
         <v>2053</v>
       </c>
@@ -27704,7 +27704,7 @@
       <c r="R38" s="23"/>
       <c r="S38" s="23"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="20">
         <v>2054</v>
       </c>
@@ -27755,7 +27755,7 @@
       <c r="R39" s="23"/>
       <c r="S39" s="23"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="20">
         <v>2055</v>
       </c>
@@ -27806,7 +27806,7 @@
       <c r="R40" s="23"/>
       <c r="S40" s="23"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="20">
         <v>2056</v>
       </c>
@@ -27857,7 +27857,7 @@
       <c r="R41" s="23"/>
       <c r="S41" s="23"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="20">
         <v>2057</v>
       </c>
@@ -27908,7 +27908,7 @@
       <c r="R42" s="23"/>
       <c r="S42" s="23"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="20">
         <v>2058</v>
       </c>
@@ -27959,7 +27959,7 @@
       <c r="R43" s="23"/>
       <c r="S43" s="23"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="20">
         <v>2059</v>
       </c>
@@ -28010,7 +28010,7 @@
       <c r="R44" s="23"/>
       <c r="S44" s="23"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="20">
         <v>2060</v>
       </c>
@@ -28061,7 +28061,7 @@
       <c r="R45" s="23"/>
       <c r="S45" s="23"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="20">
         <v>2061</v>
       </c>
@@ -28112,7 +28112,7 @@
       <c r="R46" s="23"/>
       <c r="S46" s="23"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="20">
         <v>2062</v>
       </c>
@@ -28163,7 +28163,7 @@
       <c r="R47" s="23"/>
       <c r="S47" s="23"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="20">
         <v>2063</v>
       </c>
@@ -28214,7 +28214,7 @@
       <c r="R48" s="23"/>
       <c r="S48" s="23"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="20">
         <v>2064</v>
       </c>
@@ -28265,7 +28265,7 @@
       <c r="R49" s="23"/>
       <c r="S49" s="23"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" s="20">
         <v>2065</v>
       </c>
@@ -28316,7 +28316,7 @@
       <c r="R50" s="23"/>
       <c r="S50" s="23"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="20">
         <v>2066</v>
       </c>
@@ -28367,7 +28367,7 @@
       <c r="R51" s="23"/>
       <c r="S51" s="23"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" s="20">
         <v>2067</v>
       </c>
@@ -28418,7 +28418,7 @@
       <c r="R52" s="23"/>
       <c r="S52" s="23"/>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" s="20">
         <v>2068</v>
       </c>
@@ -28469,7 +28469,7 @@
       <c r="R53" s="23"/>
       <c r="S53" s="23"/>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" s="20">
         <v>2069</v>
       </c>
@@ -28520,7 +28520,7 @@
       <c r="R54" s="23"/>
       <c r="S54" s="23"/>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" s="20">
         <v>2070</v>
       </c>
@@ -28571,7 +28571,7 @@
       <c r="R55" s="23"/>
       <c r="S55" s="23"/>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" s="20">
         <v>2071</v>
       </c>
@@ -28622,7 +28622,7 @@
       <c r="R56" s="23"/>
       <c r="S56" s="23"/>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" s="20">
         <v>2072</v>
       </c>
@@ -28673,7 +28673,7 @@
       <c r="R57" s="23"/>
       <c r="S57" s="23"/>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" s="20">
         <v>2073</v>
       </c>
@@ -28724,7 +28724,7 @@
       <c r="R58" s="23"/>
       <c r="S58" s="23"/>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="20">
         <v>2074</v>
       </c>
@@ -28775,7 +28775,7 @@
       <c r="R59" s="23"/>
       <c r="S59" s="23"/>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="20">
         <v>2075</v>
       </c>
@@ -28826,7 +28826,7 @@
       <c r="R60" s="23"/>
       <c r="S60" s="23"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="20">
         <v>2076</v>
       </c>
@@ -28877,7 +28877,7 @@
       <c r="R61" s="23"/>
       <c r="S61" s="23"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="20">
         <v>2077</v>
       </c>
@@ -28928,7 +28928,7 @@
       <c r="R62" s="23"/>
       <c r="S62" s="23"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="20">
         <v>2078</v>
       </c>
@@ -28979,7 +28979,7 @@
       <c r="R63" s="23"/>
       <c r="S63" s="23"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="20">
         <v>2079</v>
       </c>
@@ -29030,7 +29030,7 @@
       <c r="R64" s="23"/>
       <c r="S64" s="23"/>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="20">
         <v>2080</v>
       </c>
@@ -29081,7 +29081,7 @@
       <c r="R65" s="23"/>
       <c r="S65" s="23"/>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="20">
         <v>2081</v>
       </c>
@@ -29132,7 +29132,7 @@
       <c r="R66" s="23"/>
       <c r="S66" s="23"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="20">
         <v>2082</v>
       </c>
@@ -29183,7 +29183,7 @@
       <c r="R67" s="23"/>
       <c r="S67" s="23"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="20">
         <v>2083</v>
       </c>
@@ -29234,7 +29234,7 @@
       <c r="R68" s="23"/>
       <c r="S68" s="23"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="20">
         <v>2084</v>
       </c>
@@ -29285,7 +29285,7 @@
       <c r="R69" s="23"/>
       <c r="S69" s="23"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="20">
         <v>2085</v>
       </c>
@@ -29336,7 +29336,7 @@
       <c r="R70" s="23"/>
       <c r="S70" s="23"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="20">
         <v>2086</v>
       </c>
@@ -29387,7 +29387,7 @@
       <c r="R71" s="23"/>
       <c r="S71" s="23"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="20">
         <v>2087</v>
       </c>
@@ -29438,7 +29438,7 @@
       <c r="R72" s="23"/>
       <c r="S72" s="23"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" s="20">
         <v>2088</v>
       </c>
@@ -29489,7 +29489,7 @@
       <c r="R73" s="23"/>
       <c r="S73" s="23"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="20">
         <v>2089</v>
       </c>
@@ -29540,7 +29540,7 @@
       <c r="R74" s="23"/>
       <c r="S74" s="23"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="20">
         <v>2090</v>
       </c>
@@ -29591,7 +29591,7 @@
       <c r="R75" s="23"/>
       <c r="S75" s="23"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="20">
         <v>2091</v>
       </c>
@@ -29642,7 +29642,7 @@
       <c r="R76" s="23"/>
       <c r="S76" s="23"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="20">
         <v>2092</v>
       </c>
@@ -29693,7 +29693,7 @@
       <c r="R77" s="23"/>
       <c r="S77" s="23"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="20">
         <v>2093</v>
       </c>
@@ -29744,7 +29744,7 @@
       <c r="R78" s="23"/>
       <c r="S78" s="23"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="20">
         <v>2094</v>
       </c>
@@ -29795,7 +29795,7 @@
       <c r="R79" s="23"/>
       <c r="S79" s="23"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" s="20">
         <v>2095</v>
       </c>
@@ -29846,7 +29846,7 @@
       <c r="R80" s="23"/>
       <c r="S80" s="23"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" s="20">
         <v>2096</v>
       </c>
@@ -29897,7 +29897,7 @@
       <c r="R81" s="23"/>
       <c r="S81" s="23"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" s="20">
         <v>2097</v>
       </c>
@@ -29948,7 +29948,7 @@
       <c r="R82" s="23"/>
       <c r="S82" s="23"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" s="20">
         <v>2098</v>
       </c>
@@ -29999,7 +29999,7 @@
       <c r="R83" s="23"/>
       <c r="S83" s="23"/>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" s="20">
         <v>2099</v>
       </c>
@@ -30050,7 +30050,7 @@
       <c r="R84" s="23"/>
       <c r="S84" s="23"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" s="20">
         <v>2100</v>
       </c>
@@ -30101,7 +30101,7 @@
       <c r="R85" s="23"/>
       <c r="S85" s="23"/>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" s="20"/>
       <c r="B86" s="23"/>
       <c r="C86" s="23"/>
@@ -30133,22 +30133,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8944EF0B-4042-4779-82CE-4B05AD3AA32F}">
   <dimension ref="A1:J86"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7265625" customWidth="1"/>
+    <col min="7" max="8" width="18.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>1</v>
@@ -30160,19 +30160,19 @@
         <v>50</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I1" s="24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J1" s="24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>20</v>
       </c>
@@ -30204,15 +30204,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="33" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>12</v>
@@ -30221,22 +30221,22 @@
         <v>12</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J3" s="34" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="35" t="s">
         <v>23</v>
       </c>
@@ -30250,7 +30250,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="35">
         <v>2020</v>
       </c>
@@ -30282,7 +30282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="35">
         <v>2021</v>
       </c>
@@ -30314,7 +30314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -30346,7 +30346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="35">
         <v>2023</v>
       </c>
@@ -30378,7 +30378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="35">
         <v>2024</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="23">
         <v>2025</v>
       </c>
@@ -30442,7 +30442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="23">
         <v>2026</v>
       </c>
@@ -30474,7 +30474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="23">
         <v>2027</v>
       </c>
@@ -30506,7 +30506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="23">
         <v>2028</v>
       </c>
@@ -30538,7 +30538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="23">
         <v>2029</v>
       </c>
@@ -30570,7 +30570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="23">
         <v>2030</v>
       </c>
@@ -30602,7 +30602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="23">
         <v>2031</v>
       </c>
@@ -30634,7 +30634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="23">
         <v>2032</v>
       </c>
@@ -30666,7 +30666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="23">
         <v>2033</v>
       </c>
@@ -30698,7 +30698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="23">
         <v>2034</v>
       </c>
@@ -30730,7 +30730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="23">
         <v>2035</v>
       </c>
@@ -30762,7 +30762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="23">
         <v>2036</v>
       </c>
@@ -30794,7 +30794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="23">
         <v>2037</v>
       </c>
@@ -30826,7 +30826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="23">
         <v>2038</v>
       </c>
@@ -30858,7 +30858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="23">
         <v>2039</v>
       </c>
@@ -30890,7 +30890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="23">
         <v>2040</v>
       </c>
@@ -30922,7 +30922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="23">
         <v>2041</v>
       </c>
@@ -30954,7 +30954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="23">
         <v>2042</v>
       </c>
@@ -30986,7 +30986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="23">
         <v>2043</v>
       </c>
@@ -31018,7 +31018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="23">
         <v>2044</v>
       </c>
@@ -31050,7 +31050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="23">
         <v>2045</v>
       </c>
@@ -31082,7 +31082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="23">
         <v>2046</v>
       </c>
@@ -31114,7 +31114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="23">
         <v>2047</v>
       </c>
@@ -31146,7 +31146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="23">
         <v>2048</v>
       </c>
@@ -31178,7 +31178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="23">
         <v>2049</v>
       </c>
@@ -31210,7 +31210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="23">
         <v>2050</v>
       </c>
@@ -31242,7 +31242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="23">
         <v>2051</v>
       </c>
@@ -31274,7 +31274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="23">
         <v>2052</v>
       </c>
@@ -31306,7 +31306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="23">
         <v>2053</v>
       </c>
@@ -31338,7 +31338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="23">
         <v>2054</v>
       </c>
@@ -31370,7 +31370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="23">
         <v>2055</v>
       </c>
@@ -31402,7 +31402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="23">
         <v>2056</v>
       </c>
@@ -31434,7 +31434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="23">
         <v>2057</v>
       </c>
@@ -31466,7 +31466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="23">
         <v>2058</v>
       </c>
@@ -31498,7 +31498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="23">
         <v>2059</v>
       </c>
@@ -31530,7 +31530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="23">
         <v>2060</v>
       </c>
@@ -31562,7 +31562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="23">
         <v>2061</v>
       </c>
@@ -31594,7 +31594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="23">
         <v>2062</v>
       </c>
@@ -31626,7 +31626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="23">
         <v>2063</v>
       </c>
@@ -31658,7 +31658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="23">
         <v>2064</v>
       </c>
@@ -31690,7 +31690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="23">
         <v>2065</v>
       </c>
@@ -31722,7 +31722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="23">
         <v>2066</v>
       </c>
@@ -31754,7 +31754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="23">
         <v>2067</v>
       </c>
@@ -31786,7 +31786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="23">
         <v>2068</v>
       </c>
@@ -31818,7 +31818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="23">
         <v>2069</v>
       </c>
@@ -31850,7 +31850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="23">
         <v>2070</v>
       </c>
@@ -31882,7 +31882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="23">
         <v>2071</v>
       </c>
@@ -31914,7 +31914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="23">
         <v>2072</v>
       </c>
@@ -31946,7 +31946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="23">
         <v>2073</v>
       </c>
@@ -31978,7 +31978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="23">
         <v>2074</v>
       </c>
@@ -32010,7 +32010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="23">
         <v>2075</v>
       </c>
@@ -32042,7 +32042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="23">
         <v>2076</v>
       </c>
@@ -32074,7 +32074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="23">
         <v>2077</v>
       </c>
@@ -32106,7 +32106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="23">
         <v>2078</v>
       </c>
@@ -32138,7 +32138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="23">
         <v>2079</v>
       </c>
@@ -32170,7 +32170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="23">
         <v>2080</v>
       </c>
@@ -32202,7 +32202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="23">
         <v>2081</v>
       </c>
@@ -32234,7 +32234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="23">
         <v>2082</v>
       </c>
@@ -32266,7 +32266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="23">
         <v>2083</v>
       </c>
@@ -32298,7 +32298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="23">
         <v>2084</v>
       </c>
@@ -32330,7 +32330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="23">
         <v>2085</v>
       </c>
@@ -32362,7 +32362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="23">
         <v>2086</v>
       </c>
@@ -32394,7 +32394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="23">
         <v>2087</v>
       </c>
@@ -32426,7 +32426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="23">
         <v>2088</v>
       </c>
@@ -32458,7 +32458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="23">
         <v>2089</v>
       </c>
@@ -32490,7 +32490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="23">
         <v>2090</v>
       </c>
@@ -32522,7 +32522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="23">
         <v>2091</v>
       </c>
@@ -32554,7 +32554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="23">
         <v>2092</v>
       </c>
@@ -32586,7 +32586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="23">
         <v>2093</v>
       </c>
@@ -32618,7 +32618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="23">
         <v>2094</v>
       </c>
@@ -32650,7 +32650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="23">
         <v>2095</v>
       </c>
@@ -32682,7 +32682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="23">
         <v>2096</v>
       </c>
@@ -32714,7 +32714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="23">
         <v>2097</v>
       </c>
@@ -32746,7 +32746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="23">
         <v>2098</v>
       </c>
@@ -32778,7 +32778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="23">
         <v>2099</v>
       </c>
@@ -32810,7 +32810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="23">
         <v>2100</v>
       </c>
@@ -32842,7 +32842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="20"/>
       <c r="B86" s="23"/>
       <c r="C86" s="23"/>
